--- a/scripts/DoAn4_Bemori/test/cases/SCR_BinhLuan_Bemori.xlsx
+++ b/scripts/DoAn4_Bemori/test/cases/SCR_BinhLuan_Bemori.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>gấu rất đẹp</t>
+          <t>đẹp quá</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ngọc hà</t>
+          <t>nhoan</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0927856143</t>
+          <t>0123456789</t>
         </is>
       </c>
     </row>
@@ -677,11 +677,7 @@
           <t>txtNoiDungBinhLuan</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -699,7 +695,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> chinh phạm</t>
+          <t>hoan</t>
         </is>
       </c>
     </row>
@@ -719,7 +715,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0981237645</t>
+          <t>0182736459</t>
         </is>
       </c>
     </row>
@@ -861,7 +857,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>đẹp quá shop ơi</t>
+          <t>đẹp quá</t>
         </is>
       </c>
     </row>
@@ -879,11 +875,7 @@
           <t>txtHoTen</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -901,7 +893,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0981237645</t>
+          <t>0182736459</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1035,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>gấu đẹp ghê</t>
+          <t>đẹp quá</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1055,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> trang</t>
+          <t>họcn</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1213,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>xinh xỉu</t>
+          <t>đẹp quá</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1233,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> hien</t>
+          <t>lann</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1253,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> abc124%^&amp;</t>
+          <t>sodienthoai</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1395,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>gấu rất cute</t>
+          <t>đẹp quá</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1415,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> abc</t>
+          <t>nhoan</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1435,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>01928376</t>
+          <t>012345678</t>
         </is>
       </c>
     </row>
